--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/nuble.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/nuble.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9442.639999999999</v>
+        <v>9425.889999999999</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>17232.29</v>
+        <v>17201.73</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>21482.8</v>
+        <v>21205.13</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9275.780000000001</v>
+        <v>9259.879999999999</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8786.120000000001</v>
+        <v>8724.120000000001</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>11406.98</v>
+        <v>11376.81</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/nuble.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/nuble.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ñuble" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1079580-493-CM25</t>
+          <t>229-432-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>69.141.100-1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,43 +569,43 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9425.889999999999</v>
+        <v>27067.96</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1079580-495-CM25</t>
+          <t>1375761-56-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.000.520-7</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+          <t>IGMA CONSULTORES LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15.888.842-4</t>
+          <t>76.465.697-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,43 +630,43 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>17201.73</v>
+        <v>10151.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4594-1198-CM25</t>
+          <t>1052231-109-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.141.102-8</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>21205.13</v>
+        <v>5753.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2467-56-CM26</t>
+          <t>1079580-493-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SECCIÓN COMPRAS XVI ZONA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA MUEBLES ASENJO LIMITADA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.208.692-K</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9259.879999999999</v>
+        <v>9425.889999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3785-40-CM26</t>
+          <t>1079580-495-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>62.000.520-7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>SECCIÓN COMPRAS XVI ZONA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8724.120000000001</v>
+        <v>17201.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2727-512-CM26</t>
+          <t>4594-1198-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.141.102-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,7 +874,251 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
+        <v>21205.13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2467-56-CM26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.140.900-7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>77.208.692-K</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>9259.879999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3785-40-CM26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.150.200-7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>INDUMAC LTDA.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>83.732.700-8</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>8724.120000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2727-512-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.140.500-1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>COMERCIAL RENHET SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>77.619.564-2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
         <v>11376.81</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1233616-1463-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>27851.72</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/nuble.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -880,7 +880,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2467-56-CM26</t>
+          <t>1375761-13-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.981.330-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA MUEBLES ASENJO LIMITADA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.208.692-K</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9259.879999999999</v>
+        <v>20755.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3785-40-CM26</t>
+          <t>2467-56-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.150.200-7</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COELEMU</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>DISTRIBUIDORA MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
+          <t>77.208.692-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8724.120000000001</v>
+        <v>9259.879999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2727-512-CM26</t>
+          <t>3785-40-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>69.150.200-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>I MUNICIPALIDAD DE COELEMU</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIAL RENHET SPA</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.619.564-2</t>
+          <t>83.732.700-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11376.81</v>
+        <v>8724.120000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1233616-1463-CM26</t>
+          <t>2727-512-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.980.940-8</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL RENHET SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>77.619.564-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,6 +1118,189 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
+        <v>11376.81</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1069417-850-CM26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>69.270.200-k</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>IMPORTADORA FULLMUEBLES SPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>77.351.814-9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>7702.74</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1375761-1330-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.981.330-8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE DIGUILLÍN</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>17443.73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1233616-1463-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
         <v>27851.72</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/nuble.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/nuble.xlsx
@@ -623,7 +623,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>77.351.814-9</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/nuble.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/nuble.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1340,6 +1340,197 @@
         <v>27851.72</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1059240-60-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.935.400-1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MINISTERIO PUBLICO</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>9464.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1036569-158-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>62.000.390-5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ÑUBLE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>JUEGOS MAGICOS</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.102.918-5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>42677.44</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1233616-1907-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.980.940-8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>12551.44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/nuble.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/nuble.xlsx
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
